--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rfd7eac3916b04394"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Ra95d009658204167"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Ra95d009658204167"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R2b1f7f86d9bb401a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -348,15 +348,15 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>虚构并脱敏的账号接管调查演练数据</x:v>
+        <x:v>本次账号接管调查使用的设备关联数据，字段已经脱敏</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>数据装载</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>从输入数据包解压后直接读取input_data目录</x:v>
+        <x:v>入口复制risk_graph.db，将graph_policy.json和action_routes.csv装入同一SQLite连接，再执行完成版SQL</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="32" customHeight="1">
@@ -377,10 +377,10 @@
     </x:row>
     <x:row r="9" ht="32" customHeight="1">
       <x:c r="A9" s="9" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>调查目标</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>装载策略与动作路由，筛选关系并展开双向边，递归生成无环候选路径，裁决最佳路径，计算风险分，选择动作档位，连接团队路由并导出报告</x:v>
+        <x:v>从高风险种子沿合格设备关系追踪关联账号和设备，保留最佳证据路径，并把达到门槛的设备分派给对应处置团队</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
@@ -433,34 +433,34 @@
     </x:row>
     <x:row r="16" ht="32" customHeight="1">
       <x:c r="A16" s="5" t="str">
-        <x:v>源数据保护</x:v>
+        <x:v>SQLite执行边界</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
-        <x:v>四张源表保留原内容，运行不得覆盖输入数据库和规则文件</x:v>
+        <x:v>关系裁决、递归路径、风险计算和动作分档都在SQLite中完成，Node.js只负责复制数据库、装载规则和导出报告</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="32" customHeight="1">
       <x:c r="A17" s="9" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>调查库交付</x:v>
       </x:c>
       <x:c r="B17" s="9" t="str">
-        <x:v>派生数据库完整，五个交付文件齐全，关系、路径、分数、队列与路由跨产物一致</x:v>
+        <x:v>device_risk_review.db保留四张源表，并写入动作路由、拒绝关系、合格边、有效种子、最佳路径、账号风险和处置队列</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="32" customHeight="1">
       <x:c r="A18" s="5" t="str">
-        <x:v>可验证点</x:v>
+        <x:v>报告交接</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
-        <x:v>源表逐行对照；SQLite完整性；拒绝主键集合；路径联合主键；风险分容差；队列顺序；路由字段</x:v>
+        <x:v>risk_paths.csv供调查员查看传播证据，action_queue.csv供处置组接单，rejected_links.csv供数据团队检查过滤关系</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="32" customHeight="1">
       <x:c r="A19" s="10" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
+        <x:v>等价实现边界</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>SQL缩进、注释、CTE拆分、临时对象名、SQLite页布局、非业务行序及CSV换行符</x:v>
+        <x:v>SQL可以调整CTE拆分、临时对象名、注释和索引；数据库业务表、报告字段、主键集合、路径裁决、数值精度和队列顺序保持一致</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
